--- a/important_mails_2026-05-08.xlsx
+++ b/important_mails_2026-05-08.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H157"/>
+  <dimension ref="A1:H165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -537,12 +537,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -552,21 +552,391 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Thu, 7 May 2026 18:10:42 +0000</t>
+          <t>Fri, 8 May 2026 11:37:14 +0000</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>donotreply@amazon.com</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Your FBA request is complete (toabAY9R4I)</t>
+          <t>Votre facture pour les frais de paiement au titre de la REP pour
+ les ventes sur Amazon.fr |   Your VAT invoice for EPR Pay on Behalf charges
+ for Amazon.fr sales</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Bonjour,
+Votre facture pour couvrant les frais de paiement au titre de la Responsabilité élargie du producteur (REP) pour les ventes sur Amazon.fr est désormais disponible.
+La facture comprend (1) les frais d’éco-contribution qu’Amazon a payé en votre nom pour les ventes de produits soumis à des obligations REP sur Amazon.fr au cours de la période de référence applicable et (2) les frais de service REP Nous payons en votre nom, pour les catégories de REP spécifiées dans le résumé au niveau de la catégorie et dans le résumé au niveau de l’ASIN.
+Pour accéder à votre facture REP Nous Payons en votre nom , ouvrez la pièce jointe de cet e-mail ou accédez à la section Factures des frais du vendeur et recherchez « REP Nous payons en votre nom » dans la colonne « Type de facture ».
+Pour afficher un résumé au niveau de la catégorie des frais facturés, des périodes de déclaration applicables et des catégories REP, accédez à la section Affichage des transactions avec les frais de service comme type de transaction, et recherchez « REP Nous payons en votre nom » dans la colonne « Détails sur le produit ».
+Pour afficher le détail au niveau de l’ASIN de vos frais d’éco-contribution REP, des pério</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 14:40:42 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Je Factuur Verkoper Amazon.com.be voor 4/2026 (Votre Facture
+ Vendeur Amazon.com.be pour le mois de 4/2026)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
+We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
+Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
+In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
+Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
+Met vriendelijke groeten,
+Amazon.com.be
+ Monsieur/Madame Shen zhen shi wei hai zhong xin ke ji you xian,
+Nous vous écrivons pour vous informer que votre Facture Vendeur pour le mois de 4/2026 est maintenant disponible dans votre compte Seller Central.
+Pour accéder à votre facture, rendez-vous sur votre compte Seller Central et veuillez accéder à la page Rapports &gt; Bibliothèque d'informations fiscales &gt; Factures des frais du vendeur.
+Dans votre compte Seller Central, vous pourrez afficher, télécharger ou imprimer votre facture.
+Pour toute question, contactez le Support Vendeur.
+Cordialement,
+Amazon.com.be</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 13:57:28 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.co.uk Merchant Invoice for 4/2026</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your invoice.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.co.uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 13:43:13 +0000</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
+Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
+För att komma åt ditt fakturagår du till ditt Seller Central-konto &gt; Rapporter &gt; Bibliotek för skattedokument &gt; Skattefakturor för säljaravgifter.
+På ditt Seller Central-konto kan du se, ladda ner eller skriva ut ditt faktura.
+Om du har några frågor, kontakta säljarsupport.
+Vänliga hälsningar,
+Amazon.se</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 13:40:52 +0000</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 11:55:06 +0000</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 4.2026</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 11:49:29 +0000</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 4/2026</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 4/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your invoice.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.co.uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 11:20:15 +0000</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Dein Einkaufswagen wartet</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
+Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
+ 23,49 €
+https://www.amazon.de/gp/product/B0DRCB74YN/?ref_=
+Einkaufswagen anzeigen
+https://www.amazon.de/gp/cart/view.html?ref_=cor
+Schaue dir weitere Optionen an
+75x120 cm Feuerfeste Unterlage, Hitzeschutzmatte, Antihaft-Material Bodenschutzmatte, Grill Matten, Bodenmatte Feuerstellenmatte Outdoor BBQ Matte für Gasgrill Holzkohlegrill
+ 16,80 €
+https://www.amazon.de/gp/product/B0DBLM41YS/?ref_=ci_mcx_mr_2p_0_lm
+100 * 150cm Feuerfeste Unterlage - Hitzebeständig bis 1800°F Hitzeschutzmatte - Grillteppich Bodenschutzmatte Grillmatten Bodenmatte Feuerstellenmatte Outdoor BBQ Matte für Gasgrill Holzkohlegrill
+ -17 % 25,19 € UVP: 30,24 €
+https://www.amazon.de/gp/product/B0BRTPDYMV/?ref_=ci_mcx_mr_2p_1_lm
+Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
+ -4 % 20,15 € UVP: 20,97 €
+https://www.amazon.de/gp/product/B0CSGBZG8W/?ref_=ci_mc</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 7 May 2026 18:10:42 +0000</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (toabAY9R4I)</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -586,39 +956,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 11:59:35 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cp3IU6ppnV)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -638,39 +1008,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 16:07:01 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -691,39 +1061,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 13:03:07 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (2604121A02)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -743,39 +1113,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Mon, 4 May 2026 16:59:42 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (AOOD6vlnxr)</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -795,39 +1165,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:32:02 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $69.79 in an attempt to settle your Amazon seller account balance.
@@ -843,91 +1213,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 1 May 2026 07:28:26 +0000</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA request is complete (5NT+O11io4)</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral-europe.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-1039400-9149300
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
-------------------------------------------------------------------------------
-Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
-and EU wide.
-------------------------------------------------------------------------------
-Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-EUAmazon-1196270299109386</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:42 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -944,39 +1262,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:28 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -996,39 +1314,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:01:21 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1048,39 +1366,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 03:44:19 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1097,39 +1415,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 15:00:39 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 87.72 in an attempt to settle your account balance.
@@ -1144,39 +1462,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:45:41 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -1192,39 +1510,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:23:38 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>欧洲亚马逊 Payments &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>跨账户负余额调整</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1244,39 +1562,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1296,140 +1614,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 1 May 2026 14:27:01 +0000</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Tu pago está en camino</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- ¡Enhorabuena! El pago está de camino y llegará pronto.
- El pago está en camino
-Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
-El 05/01/26 14:26 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
- 302,19.
- Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
- ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
- ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
-Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
-Te deseamos un éx</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 1 May 2026 14:26:48 +0000</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement Attempted
-Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
-On 05/01/26 14:26 CEST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of €
- 315.67.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon store,
-Amazon Services
-Help us improve your payment experience on Ama</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 17:50:39 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -1448,39 +1665,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 12:49:24 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1504,39 +1721,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 02:13:07 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1554,39 +1771,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 13:18:47 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1604,39 +1821,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 13:15:01 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1654,39 +1871,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:13:49 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1704,137 +1921,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 1 May 2026 14:19:29 +0000</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 6 May 2026 15:00:42 +0000</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 1 May 2026 12:52:07 +0000</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon-Fulfilled Inventory - Action Required</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Dear Seller,
-You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
-Please create a removal request for the ASIN(s) listed below to have your inventory sent to a location of your choice. If this inventory is not removed within 30 days of this notification (by 30/05/2026), we shall dispose of it in accordance with our FBA policies.
-For more information regarding the removal of this product, see the notification e-mail you received from our Seller Performance Team.
-Thank you for your prompt attention to this matter.
-Yours faithfully,
-Fulfilment by Amazon Team
-Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
-Affected Product(s):
-B0FPC87B1W
- SPC-EUAmazon-1301823416934708</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 6 May 2026 15:00:42 +0000</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1849,39 +1968,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 14:24:59 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 4/2026 (Amazon.ae فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 4/2026)</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -1900,39 +2019,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 05:32:15 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -1954,39 +2073,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:27:47 +0600</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Deals &lt;amazonreviewsdeals1@gmail.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Rating Deals</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Not getting sales on Amazon? Even after doing everything right? Then this
 message is for you!
@@ -2012,40 +2131,40 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 03:15:52 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -2061,40 +2180,40 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:51 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -2110,39 +2229,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:45 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -2158,39 +2277,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 01:23:15 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -2206,39 +2325,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 15:09:15 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -2254,85 +2373,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 1 May 2026 14:16:19 +0000</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
- Dzień dobry Weihai EU,
- niektóre z Twoich ofert zostały zdezaktywowane z powodu niespełnienia obowiązków dotyczących zgodności wystawianych przez Ciebie produktów z wymogami. Poniżej znajdziesz szczegółowe informacje oraz dalsze instrukcje. Oferty produktów, których dotyczy problem, wskazano na końcu niniejszej wiadomości e-mail.
- Dlaczego tak się stało?
- Podjęliśmy to działanie, ponieważ w przypadku tych produktów nie dostarczono obowiązkowych informacji dotyczących zgodności z wymogami. Więcej informacji na temat mających zastosowanie przepisów ustawowych i wykonawczych oraz zasad Amazon znajdziesz na stronie Bezpieczeństwo i zgodność produktu z wymogami . Do identyfikacji problemu i podjęcia decyzji wykorzystaliśmy zautomatyzowane narzędzia, a otrzymane za ich pomocą wyniki poddaliśmy weryfikacji przez eksperta.
- Informacje na temat wymogów dotyczących zgodności dla poszczególnych produktów znajdziesz w tabeli na końcu tej wiadomości e-mail.
- Jak mogę ponownie aktywować oferty?
- Aby dostarczyć niezbędne informacje dotyczące zgodności z wymogami, przejdź do panelu Kondycja konta i </t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 04:46:00 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2356,39 +2429,91 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 1 May 2026 07:28:26 +0000</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (5NT+O11io4)</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral-europe.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-1039400-9149300
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+------------------------------------------------------------------------------
+Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
+and EU wide.
+------------------------------------------------------------------------------
+Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-EUAmazon-1196270299109386</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:54:23 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $44.85 in an attempt to settle your Amazon seller account balance.
@@ -2404,39 +2529,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 04:59:05 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (26041219YV)</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2456,39 +2581,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2514,39 +2639,140 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 1 May 2026 14:27:01 +0000</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Tu pago está en camino</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ ¡Enhorabuena! El pago está de camino y llegará pronto.
+ El pago está en camino
+Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
+El 05/01/26 14:26 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
+ 302,19.
+ Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
+ ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
+ ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
+Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
+Te deseamos un éx</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 1 May 2026 14:26:48 +0000</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
+On 05/01/26 14:26 CEST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of €
+ 315.67.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+Help us improve your payment experience on Ama</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 17:03:06 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2566,39 +2792,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:56 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2615,39 +2841,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:50 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2667,39 +2893,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 05:12:21 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;seller-notification@amazon.ie&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Outstanding balance on your Amazon account</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Hello,
  You have an outstanding balance on your account in the amount of 7,79 EUR. We will debit this amount from the credit card (Visa) that you registered as the charge method for your account.
@@ -2713,39 +2939,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 15:01:26 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2765,39 +2991,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 14:27:43 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2814,39 +3040,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -2862,39 +3088,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:44:32 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2914,39 +3140,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:38:30 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2963,39 +3189,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Cher vendeur,
  Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
@@ -3007,39 +3233,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Negative balance adjustment across your Selling on Amazon accounts</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3062,39 +3288,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Apr 2026 15:29:23 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3118,39 +3344,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 14:28:35 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 62.05 in an attempt to settle your account balance.
@@ -3165,39 +3391,137 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 1 May 2026 14:19:29 +0000</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 1 May 2026 12:52:07 +0000</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon-Fulfilled Inventory - Action Required</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Dear Seller,
+You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
+Please create a removal request for the ASIN(s) listed below to have your inventory sent to a location of your choice. If this inventory is not removed within 30 days of this notification (by 30/05/2026), we shall dispose of it in accordance with our FBA policies.
+For more information regarding the removal of this product, see the notification e-mail you received from our Seller Performance Team.
+Thank you for your prompt attention to this matter.
+Yours faithfully,
+Fulfilment by Amazon Team
+Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
+Affected Product(s):
+B0FPC87B1W
+ SPC-EUAmazon-1301823416934708</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:11:27 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3215,39 +3539,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:14:16 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3265,39 +3589,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 13:03:36 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -3307,39 +3631,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 09:05:17 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>【请勿回复此日志，如有问题请加入下方邮件中的企微群】
 卖家您好，
@@ -3360,39 +3684,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:13:11 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -3408,39 +3732,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:52:19 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -3459,39 +3783,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 03:13:33 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20093870001] Other account issues</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Hello from Amazon Selling Partner Support,
 My name is Ritam. I am a Live Channel Specialist and I'm contacting you to follow up on your concern regarding the reinstatement of your listing B0FCDRNTT8.
@@ -3502,39 +3826,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 17:15:23 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3553,39 +3877,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:37 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3604,39 +3928,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:18 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3655,39 +3979,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 03:03:00 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -3707,39 +4031,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 01:27:00 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20061337331] 对危险品分类提出异议</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商:您好!
 我们了解到您希望重新激活商品 ASIN: B0FCDRNTT8。
@@ -3768,39 +4092,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 10:07:05 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3818,39 +4142,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:15:48 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3868,39 +4192,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:08:57 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3918,39 +4242,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 06:10:23 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>"compliance-ops-mass-programs@amazon.com" &lt;compliance-ops-mass-programs@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12449434352] 【邀请函】诚邀您参与亚马逊卖家合规策略调研</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴，
 您好！
@@ -3964,39 +4288,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 21:09:24 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4014,40 +4338,40 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 14:16:35 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4064,40 +4388,40 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 09:57:17 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4114,39 +4438,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 16:06:35 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>苏浩然 &lt;suhr@cvc.org.cn&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Amazon DV TIC</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，您好。
 我们可以为您提供亚马逊DV验证报告服务。
@@ -4180,39 +4504,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 10:14:18 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -4227,39 +4551,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 03:38:27 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -4275,39 +4599,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 11:22:53 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您在【欧洲】站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】或【已通过】。
@@ -4331,39 +4655,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 17:53:23 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4382,39 +4706,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 09:10:03 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -4430,39 +4754,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 07:35:31 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK
 [Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EMUSSMX-PD25/7z2r9lq/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA)
@@ -4474,39 +4798,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 06:23:28 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -4526,39 +4850,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Sun, 12 Apr 2026 09:09:25 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4576,40 +4900,40 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 15:28:03 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4627,39 +4951,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 12:03:53 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -4679,39 +5003,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:50:30 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -4732,39 +5056,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:38:53 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -4785,40 +5109,40 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:23:33 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>The Amazon Europe team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>VAT Calculation Services will calculate VAT by shipment as of June
  1</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
  New tax calculation method ensures compliance with European e-invoicing mandates.
@@ -4834,39 +5158,85 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 1 May 2026 14:16:19 +0000</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
+ Dzień dobry Weihai EU,
+ niektóre z Twoich ofert zostały zdezaktywowane z powodu niespełnienia obowiązków dotyczących zgodności wystawianych przez Ciebie produktów z wymogami. Poniżej znajdziesz szczegółowe informacje oraz dalsze instrukcje. Oferty produktów, których dotyczy problem, wskazano na końcu niniejszej wiadomości e-mail.
+ Dlaczego tak się stało?
+ Podjęliśmy to działanie, ponieważ w przypadku tych produktów nie dostarczono obowiązkowych informacji dotyczących zgodności z wymogami. Więcej informacji na temat mających zastosowanie przepisów ustawowych i wykonawczych oraz zasad Amazon znajdziesz na stronie Bezpieczeństwo i zgodność produktu z wymogami . Do identyfikacji problemu i podjęcia decyzji wykorzystaliśmy zautomatyzowane narzędzia, a otrzymane za ich pomocą wyniki poddaliśmy weryfikacji przez eksperta.
+ Informacje na temat wymogów dotyczących zgodności dla poszczególnych produktów znajdziesz w tabeli na końcu tej wiadomości e-mail.
+ Jak mogę ponownie aktywować oferty?
+ Aby dostarczyć niezbędne informacje dotyczące zgodności z wymogami, przejdź do panelu Kondycja konta i </t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:33:13 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 04/2026</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -4884,40 +5254,40 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:34 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -4933,39 +5303,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:30 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -4981,39 +5351,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:21:43 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -5029,40 +5399,40 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:18:50 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -5078,39 +5448,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:55:17 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -5127,39 +5497,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:32:46 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -5188,39 +5558,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 15:08:42 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -5236,39 +5606,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:12:49 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -5282,39 +5652,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:07:32 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5329,39 +5699,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 10:18:53 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -5381,39 +5751,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 20:59:56 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para mayo</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para mayo
@@ -5442,40 +5812,40 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:37:52 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Il team di Gestione multicanale &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Aggiornamenti ai costi di Gestione multicanale in vigore dal 29
  maggio 2026</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
  Stiamo aggiornando le tariffe di Gestione multicanale per aiutarti a ridurre i costi e investire nella crescita della tua attività.
@@ -5488,39 +5858,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:30:37 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>The Multichannel Fulfillment team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>MCF fee updates effective May 29, 2026</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  We’re updating our Multichannel Fulfillment fees to help you reduce your costs so you can invest in growing your business.
@@ -5535,39 +5905,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:25:56 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>El Departamento de Logística Multicanal &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Actualización de las tarifas de Logística Multicanal en vigor a partir del 29 de mayo de 2026</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
  Vamos a actualizar nuestras tarifas de Logística Multicanal para ayudarte a reducir los costes y así puedas invertir en hacer crecer tu negocio.
@@ -5580,40 +5950,40 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:38:42 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Presenta documentos de cumplimiento normativo del producto para
  evitar que se retiren los listings</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta documentos de cumplimiento normativo del producto para evitar que se retiren los listings
@@ -5628,40 +5998,40 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:25:34 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Documenten over productconformiteit indienen om verwijdering van
  productvermeldingen te voorkomen</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
  Documenten over productconformiteit indienen om verwijdering van productvermeldingen te voorkomen
@@ -5675,39 +6045,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:06:50 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty
@@ -5721,39 +6091,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:58:32 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort
@@ -5768,39 +6138,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:54:06 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte
@@ -5814,39 +6184,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:50:08 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente
@@ -5861,39 +6231,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 15:58:40 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5908,39 +6278,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Apr 2026 05:22:10 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -5959,39 +6329,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 11:10:42 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6007,39 +6377,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 05:38:32 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -6060,39 +6430,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:19:11 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -6110,40 +6480,40 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:18:24 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -6161,39 +6531,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:32 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6210,39 +6580,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:50 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -6260,40 +6630,40 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:30 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6311,39 +6681,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:22 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -6361,39 +6731,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 00:31:36 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -6410,39 +6780,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6457,39 +6827,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 07:42:42 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6508,39 +6878,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:32:20 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Prime Day：立即提报您的促销</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>Prime Day（日期待公布）：立即提报您的促销
 尊敬的卖家，
@@ -6558,39 +6928,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:19:47 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以重新启售商品</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品安全文件以重新启售商品
@@ -6629,39 +6999,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:42 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -6677,40 +7047,40 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:14 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -6726,39 +7096,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:36 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -6774,39 +7144,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:34 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -6820,40 +7190,40 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:11:30 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -6869,39 +7239,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:09:39 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -6917,39 +7287,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 05:22:42 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -6970,39 +7340,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 15:14:51 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -7017,39 +7387,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 09:39:52 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Verify your primary operating address for tax purposes</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  Verify your primary operating address for tax purposes
@@ -7066,39 +7436,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:10:49 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>[Formal Notice – Immediate Action Required] Review and certify your business information within 10 days to avoid account deactivation</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -7112,39 +7482,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:59:02 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Verkaeuferservice &lt;merch.service05@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12354633592] 其他账户问题</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴：
 您好！
@@ -7163,40 +7533,40 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:22:14 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Product Support Team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Reduce Returns &amp; Boost Customer Satisfaction - Enrol in Amazon
  Product Support</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
  Enrol now into Amazon Product Support !
@@ -7210,40 +7580,40 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 13:44:27 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -7261,39 +7631,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 01:52:13 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 Just a short follow-up regarding the [Vergleich.org](http://Vergleich.org)
@@ -7326,39 +7696,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 17:17:52 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Introducing Global Warehousing &amp; Distribution</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
  Store inventory at origin in China with lower costs and faster speeds.
@@ -7373,39 +7743,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 16:27:24 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 3/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -7424,39 +7794,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:49:51 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -7475,39 +7845,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:53:45 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán a medida que se procesen las unidades</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
  Las tarifas por retirada y puesta de inventario a disposición de Amazon de Logística de Amazon se cobrarán ahora por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición.
@@ -7519,39 +7889,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 09:19:33 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Opłaty za usunięcie i likwidację zapasów FBA naliczane podczas przetwarzania jednostek</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
  Opłaty za wycofanie i usunięcie zapasów w ramach FBA będą teraz pobierane od każdej jednostki w momencie jej wycofania lub usunięcia.
@@ -7567,39 +7937,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 08:46:52 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Addebito delle tariffe di rimozione e per reimpiego quando le unità vengono elaborate</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
  Le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno ora addebitate per unità ogni volta che un'unità viene rimossa o destinata ad altro uso.
@@ -7611,39 +7981,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 15:00:43 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7658,39 +8028,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 04:25:43 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7714,39 +8084,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 03:35:07 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-07</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7767,39 +8137,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-30</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7821,39 +8191,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 03:30:46 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7876,39 +8246,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-23</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7929,39 +8299,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:27:29 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7984,39 +8354,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 00:16:37 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -8046,39 +8416,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 18:05:15 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>提交商品合规文件，以避免商品被移除</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品合规文件，以避免商品被移除
@@ -8127,39 +8497,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 11:41:39 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>GTTC国际业务部玩具组 &lt;gttctoy@cngttc.cn&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>AMAZON DV TIC TRF ID--Top urgently</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>Dear Vendor,        Some of your TR numbers on Amazon have been pending in our backend for a long time without timely processing. We plan to automatically clear all unresponded TR numbers in our system two days later.
 If you have any TR numbers that require sample submission for testing, please reply to this email and send us the corresponding TR numbers within two days, and contact our relevant customer service within one week to arrange sample submission.
@@ -8168,39 +8538,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 02:18:44 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -8216,39 +8586,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
 C2S2 PCP Pallet Limited Time Promotion
@@ -8264,39 +8634,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
@@ -8316,39 +8686,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.

--- a/important_mails_2026-05-08.xlsx
+++ b/important_mails_2026-05-08.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:H178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -597,22 +597,828 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>Fri, 8 May 2026 22:29:17 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 22:25:39 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
+Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
+För att komma åt ditt fakturagår du till ditt Seller Central-konto &gt; Rapporter &gt; Bibliotek för skattedokument &gt; Skattefakturor för säljaravgifter.
+På ditt Seller Central-konto kan du se, ladda ner eller skriva ut ditt faktura.
+Om du har några frågor, kontakta säljarsupport.
+Vänliga hälsningar,
+Amazon.se</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 22:10:57 +0000</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 22:09:44 +0000</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
+We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
+Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
+In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
+Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
+Met vriendelijke groeten,
+Amazon.com.be
+ Monsieur/Madame Shen zhen shi wei hai zhong xin ke ji you xian,
+Nous vous écrivons pour vous informer que votre Facture Expédié Par Amazon pour le mois de 4/2026 est maintenant disponible dans votre compte Seller Central.
+Pour accéder à votre facture, rendez-vous sur votre compte Seller Central et veuillez accéder à la page Rapports &gt; Bibliothèque d'informations fiscales &gt; Factures des frais du vendeur.
+Dans votre compte Seller Central, vous pourrez afficher, télécharger ou imprimer votre facture.
+Pour toute question, contactez le Support Vendeur.
+Cordialement,
+Amazon.com.be</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 22:01:18 +0000</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
+We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
+Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
+In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
+Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
+Met vriendelijke groeten,
+Amazon.com.be
+ Monsieur/Madame Shen zhen shi wei hai zhong xin ke ji you xian,
+Nous vous écrivons pour vous informer que votre Facture Expédié Par Amazon pour le mois de 4/2026 est maintenant disponible dans votre compte Seller Central.
+Pour accéder à votre facture, rendez-vous sur votre compte Seller Central et veuillez accéder à la page Rapports &gt; Bibliothèque d'informations fiscales &gt; Factures des frais du vendeur.
+Dans votre compte Seller Central, vous pourrez afficher, télécharger ou imprimer votre facture.
+Pour toute question, contactez le Support Vendeur.
+Cordialement,
+Amazon.com.be</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 21:25:07 +0000</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Amazon.pl – Faktura Realizacja przez Amazon za 4 2026</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
+Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 4 i rok 2026.
+Aby uzyskać dostęp do tego dokumentu typu faktura, przejdź na konto Seller Central &gt; Raporty &gt; Dokumenty podatkowe &gt; Faktury podatkowe z tytułu opłat od sprzedawcy.
+Na koncie Seller Central możesz wyświetlić, pobrać i wydrukować taki dokument (faktura).
+Jeśli masz jakieś pytania, skontaktuj się z działem pomocy dla sprzedawców.
+Pozdrawiamy,
+Amazon.pl</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 21:24:35 +0000</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your invoice.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.co.uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 21:03:04 +0000</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
+We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
+Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
+In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
+Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
+Met vriendelijke groeten,
+Amazon.nl</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 20:51:50 +0000</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
+Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
+För att komma åt ditt fakturagår du till ditt Seller Central-konto &gt; Rapporter &gt; Bibliotek för skattedokument &gt; Skattefakturor för säljaravgifter.
+På ditt Seller Central-konto kan du se, ladda ner eller skriva ut ditt faktura.
+Om du har några frågor, kontakta säljarsupport.
+Vänliga hälsningar,
+Amazon.se</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 18:44:14 +0000</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Amazon.pl – Faktura Sprzedawcy za 4 2026</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
+Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 4 i rok 2026.
+Aby uzyskać dostęp do tego dokumentu typu faktura, przejdź na konto Seller Central &gt; Raporty &gt; Dokumenty podatkowe &gt; Faktury podatkowe z tytułu opłat od sprzedawcy.
+Na koncie Seller Central możesz wyświetlić, pobrać i wydrukować taki dokument (faktura).
+Jeśli masz jakieś pytania, skontaktuj się z działem pomocy dla sprzedawców.
+Pozdrawiamy,
+Amazon.pl</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 18:35:59 +0000</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Je Factuur Verkoper Amazon.nl voor 4/2026</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
+We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
+Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
+In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
+Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
+Met vriendelijke groeten,
+Amazon.nl</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 18:24:07 +0000</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 4.2026</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 18:18:06 +0000</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Din Faktura Säljare Amazon.se för 4/2026</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
+Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
+För att komma åt ditt fakturagår du till ditt Seller Central-konto &gt; Rapporter &gt; Bibliotek för skattedokument &gt; Skattefakturor för säljaravgifter.
+På ditt Seller Central-konto kan du se, ladda ner eller skriva ut ditt faktura.
+Om du har några frågor, kontakta säljarsupport.
+Vänliga hälsningar,
+Amazon.se</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 16:33:15 +0000</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 4/2026</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your invoice.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 16:20:52 +0000</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 15:43:38 +0000</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
+We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
+Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
+In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
+Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
+Met vriendelijke groeten,
+Amazon.nl</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 15:17:48 +0000</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your invoice.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.co.uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 14:52:53 +0000</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>Fri, 8 May 2026 14:40:42 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 4/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -631,39 +1437,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:57:28 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -675,39 +1481,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:43:13 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -719,39 +1525,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:40:52 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -763,39 +1569,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:55:06 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -807,39 +1613,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:49:29 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -851,39 +1657,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:20:15 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -904,39 +1710,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 18:10:42 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (toabAY9R4I)</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -956,39 +1762,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 11:59:35 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cp3IU6ppnV)</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1008,39 +1814,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 16:07:01 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1061,39 +1867,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 13:03:07 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (2604121A02)</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1113,39 +1919,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Mon, 4 May 2026 16:59:42 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (AOOD6vlnxr)</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1165,39 +1971,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:32:02 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $69.79 in an attempt to settle your Amazon seller account balance.
@@ -1213,39 +2019,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:42 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1262,39 +2068,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:28 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1314,39 +2120,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:01:21 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1366,39 +2172,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 03:44:19 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1415,39 +2221,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 15:00:39 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 87.72 in an attempt to settle your account balance.
@@ -1462,39 +2268,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:45:41 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -1510,39 +2316,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:23:38 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>欧洲亚马逊 Payments &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>跨账户负余额调整</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1562,39 +2368,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1614,39 +2420,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 17:50:39 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -1665,39 +2471,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 12:49:24 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1721,39 +2527,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 02:13:07 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1771,39 +2577,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 13:18:47 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1821,39 +2627,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 13:15:01 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1871,39 +2677,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:13:49 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1921,39 +2727,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 15:00:42 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1968,39 +2774,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 14:24:59 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 4/2026 (Amazon.ae فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 4/2026)</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -2019,39 +2825,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 05:32:15 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -2073,39 +2879,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:27:47 +0600</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Deals &lt;amazonreviewsdeals1@gmail.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Rating Deals</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Not getting sales on Amazon? Even after doing everything right? Then this
 message is for you!
@@ -2131,40 +2937,40 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 03:15:52 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -2180,40 +2986,40 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:51 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -2229,39 +3035,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:45 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -2277,39 +3083,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 01:23:15 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -2325,87 +3131,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 1 May 2026 15:09:15 +0000</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>96
- Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
- Bonjour Weihai EU,
- Certaines de vos mises en vente ont été désactivées, car vos produits ne respectaient pas des exigences de conformité obligatoires. Consultez les détails et les étapes suivantes ci-dessous. Les produits mis en vente concernés figurent à la fin de cet e-mail.
- Pourquoi cela se produit-il ?
- Nous prenons cette mesure, car ces produits ne présentent pas les informations de conformité obligatoires. Consultez notre page d’aide Sécurité et conformité des produits pour obtenir des informations sur les lois, réglementations et politiques Amazon applicables. Nous nous sommes appuyés sur une combinaison de moyens automatisés et de contrôles menés par des personnes expérimentées pour identifier ce problème et prendre cette décision.
- Le tableau situé à la fin de cet e-mail présente les exigences de conformité spécifiques aux produits.
- Comment réactiver mes produits mis en vente ?
- Pour fournir les informations de conformité requises, accédez à la page État du compte et localisez les demandes de conformité des produits :
--
- Si vous disposez des documents requis, suivez les instructio</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 04:46:00 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2429,39 +3187,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 07:28:26 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (5NT+O11io4)</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2481,39 +3239,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:54:23 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $44.85 in an attempt to settle your Amazon seller account balance.
@@ -2529,39 +3287,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 04:59:05 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (26041219YV)</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2581,97 +3339,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed and shipped your removal
-request (W4mGNrNTVu) to the address you specified before.
-Return Summary:
-Quantity Requested: 1
-Quantity Successfully Shipped: 1
-Quantity Cancelled: 0
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral.amazon.com/
-For a complete list of inventory being shipped, go to:
-https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-5270077-7357030
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
---------------------------------------------------------------------------
-Fulfillment by Amazon, professional packing, shipping and servicing of
-online orders.
---------------------------------------------------------------------------
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-USAmazon-1477745830956980</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:27:01 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2688,39 +3388,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:26:48 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2740,39 +3440,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 17:03:06 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2792,39 +3492,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:56 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2841,39 +3541,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:50 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2893,39 +3593,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 05:12:21 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;seller-notification@amazon.ie&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Outstanding balance on your Amazon account</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Hello,
  You have an outstanding balance on your account in the amount of 7,79 EUR. We will debit this amount from the credit card (Visa) that you registered as the charge method for your account.
@@ -2939,39 +3639,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 15:01:26 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2991,39 +3691,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 14:27:43 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3040,39 +3740,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -3088,39 +3788,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:44:32 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3140,39 +3840,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:38:30 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3189,39 +3889,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Cher vendeur,
  Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
@@ -3233,39 +3933,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Negative balance adjustment across your Selling on Amazon accounts</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3288,39 +3988,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Apr 2026 15:29:23 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3344,39 +4044,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 14:28:35 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 62.05 in an attempt to settle your account balance.
@@ -3391,39 +4091,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:19:29 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3441,39 +4141,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 12:52:07 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -3489,39 +4189,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:11:27 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3539,39 +4239,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:14:16 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3589,39 +4289,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 13:03:36 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -3631,39 +4331,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 09:05:17 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>【请勿回复此日志，如有问题请加入下方邮件中的企微群】
 卖家您好，
@@ -3684,39 +4384,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:13:11 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -3732,39 +4432,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:52:19 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -3783,39 +4483,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 03:13:33 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20093870001] Other account issues</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Hello from Amazon Selling Partner Support,
 My name is Ritam. I am a Live Channel Specialist and I'm contacting you to follow up on your concern regarding the reinstatement of your listing B0FCDRNTT8.
@@ -3826,39 +4526,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 17:15:23 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3877,39 +4577,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:37 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3928,39 +4628,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:18 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3979,39 +4679,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 03:03:00 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -4031,39 +4731,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 01:27:00 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20061337331] 对危险品分类提出异议</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商:您好!
 我们了解到您希望重新激活商品 ASIN: B0FCDRNTT8。
@@ -4092,39 +4792,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 10:07:05 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -4142,39 +4842,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:15:48 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4192,39 +4892,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:08:57 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4242,39 +4942,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 06:10:23 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>"compliance-ops-mass-programs@amazon.com" &lt;compliance-ops-mass-programs@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12449434352] 【邀请函】诚邀您参与亚马逊卖家合规策略调研</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴，
 您好！
@@ -4288,39 +4988,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 21:09:24 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4338,40 +5038,40 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 14:16:35 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4388,40 +5088,40 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 09:57:17 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4438,39 +5138,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 16:06:35 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>苏浩然 &lt;suhr@cvc.org.cn&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Amazon DV TIC</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，您好。
 我们可以为您提供亚马逊DV验证报告服务。
@@ -4504,39 +5204,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 10:14:18 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -4551,39 +5251,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 03:38:27 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -4599,39 +5299,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 11:22:53 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您在【欧洲】站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】或【已通过】。
@@ -4655,39 +5355,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 17:53:23 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4706,39 +5406,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 09:10:03 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -4754,39 +5454,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 07:35:31 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK
 [Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EMUSSMX-PD25/7z2r9lq/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA)
@@ -4798,39 +5498,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 06:23:28 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -4850,39 +5550,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Sun, 12 Apr 2026 09:09:25 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4900,40 +5600,40 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 15:28:03 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4951,39 +5651,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 12:03:53 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -5003,194 +5703,87 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 8 Apr 2026 10:50:30 +0000</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>EU and UK Compliance Brief</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe
- 96
- EU and UK Compliance Brief
- To better support your compliance journey, we've prepared an overview of regulations that affect your business in Amazon’s European stores. For more information on all compliance requirements, go to
- European compliance requirements
- Country of Origin (COO), EU &amp; UK
- Am I impacted?
- Yes, if you ship across borders to customers:
- - From outside the EU into the EU through FBA Export programs (Amazon’s global program, FBA Export, Remote Fulfilment with Fulfilment by Amazon) or MFN Exports programs (Fulfilled by Merchant Export)
- - From outside the UK into the UK through FBA Export programs (Amazon’s global program, FBA Export, Remote Fulfilment with Fulfilment by Amazon) or MFN Exports programs (Fulfilled by Merchant Export)
- Consequences of not meeting the requirement:
- To avoid disruptions to your business, provide this information to your listings by June 30, 2026.
- How do I become compliant?
- You can use the Category Listings Report (CLR) to update the COO information for your existing product listings in bulk:
-- Download the CLR from the “Inventory Reports” page on Seller Central
-- Edit the Country of Origin column for all your produ</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 8 Apr 2026 10:38:53 +0000</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>EU and UK Compliance Brief</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe
- 96
- EU and UK Compliance Brief
- To better support your compliance journey, we've prepared an overview of regulations that affect your business in Amazon’s European stores. For more information on all compliance requirements, go to
- European compliance requirements
- Country of Origin (COO), EU &amp; UK
- Am I impacted?
- Yes, if you ship across borders to customers:
- - From outside the EU into the EU through FBA Export programs (Amazon’s global program, FBA Export, Remote Fulfilment with Fulfilment by Amazon) or MFN Exports programs (Fulfilled by Merchant Export)
- - From outside the UK into the UK through FBA Export programs (Amazon’s global program, FBA Export, Remote Fulfilment with Fulfilment by Amazon) or MFN Exports programs (Fulfilled by Merchant Export)
- Consequences of not meeting the requirement:
- To avoid disruptions to your business, provide this information to your listings by June 30, 2026.
- How do I become compliant?
- You can use the Category Listings Report (CLR) to update the COO information for your existing product listings in bulk:
-- Download the CLR from the “Inventory Reports” page on Seller Central
-- Edit the Country of Origin column for all your produ</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 8 Apr 2026 10:23:33 +0000</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>The Amazon Europe team &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>VAT Calculation Services will calculate VAT by shipment as of June
- 1</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 1 May 2026 15:09:15 +0000</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
- New tax calculation method ensures compliance with European e-invoicing mandates.
- Hello,
- Effective as of June 1, 2026, we’re updating Value Added Tax (VAT) Calculation Services (VCS) to comply with European e-invoicing mandates. Instead of calculating VAT per unit, VCS will calculate VAT on the total invoice amount by tax rate. This means when customers buy multiple units, the total invoice amounts may differ from current calculations.
- Depending on the sales channel (regardless of customer VAT registration), VCS will apply one of two methods:
-- Consumer website : VCS will impute VAT from the VAT-inclusive price. If multiple units are purchased, unit exclusive prices may vary.
-- Amazon Business website : VCS will derive the VAT-exclusive unit price from the VAT-inclusive unit price. VAT will be calculated on the total VAT-exclusive price by tax rate. For more information about invoice-total VAT calculations and to view examples, go to section 10: Invoice-total VAT calculation method of VAT Calculation Services methodology .
- The Amazon Europe team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notific</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+ Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
+ Bonjour Weihai EU,
+ Certaines de vos mises en vente ont été désactivées, car vos produits ne respectaient pas des exigences de conformité obligatoires. Consultez les détails et les étapes suivantes ci-dessous. Les produits mis en vente concernés figurent à la fin de cet e-mail.
+ Pourquoi cela se produit-il ?
+ Nous prenons cette mesure, car ces produits ne présentent pas les informations de conformité obligatoires. Consultez notre page d’aide Sécurité et conformité des produits pour obtenir des informations sur les lois, réglementations et politiques Amazon applicables. Nous nous sommes appuyés sur une combinaison de moyens automatisés et de contrôles menés par des personnes expérimentées pour identifier ce problème et prendre cette décision.
+ Le tableau situé à la fin de cet e-mail présente les exigences de conformité spécifiques aux produits.
+ Comment réactiver mes produits mis en vente ?
+ Pour fournir les informations de conformité requises, accédez à la page État du compte et localisez les demandes de conformité des produits :
+-
+ Si vous disposez des documents requis, suivez les instructio</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:16:19 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -5204,39 +5797,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:33:13 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 04/2026</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -5254,40 +5847,40 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:34 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -5303,39 +5896,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:30 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -5351,39 +5944,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:21:43 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -5399,40 +5992,40 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:18:50 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -5448,39 +6041,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:55:17 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -5497,39 +6090,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:32:46 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -5558,39 +6151,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 15:08:42 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -5606,39 +6199,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:12:49 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -5652,39 +6245,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:07:32 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5699,39 +6292,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 10:18:53 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -5751,39 +6344,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 20:59:56 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para mayo</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para mayo
@@ -5812,40 +6405,40 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:37:52 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Il team di Gestione multicanale &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Aggiornamenti ai costi di Gestione multicanale in vigore dal 29
  maggio 2026</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
  Stiamo aggiornando le tariffe di Gestione multicanale per aiutarti a ridurre i costi e investire nella crescita della tua attività.
@@ -5858,39 +6451,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:30:37 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>The Multichannel Fulfillment team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>MCF fee updates effective May 29, 2026</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  We’re updating our Multichannel Fulfillment fees to help you reduce your costs so you can invest in growing your business.
@@ -5905,39 +6498,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:25:56 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>El Departamento de Logística Multicanal &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Actualización de las tarifas de Logística Multicanal en vigor a partir del 29 de mayo de 2026</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
  Vamos a actualizar nuestras tarifas de Logística Multicanal para ayudarte a reducir los costes y así puedas invertir en hacer crecer tu negocio.
@@ -5950,40 +6543,40 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:38:42 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Presenta documentos de cumplimiento normativo del producto para
  evitar que se retiren los listings</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta documentos de cumplimiento normativo del producto para evitar que se retiren los listings
@@ -5998,40 +6591,40 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:25:34 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Documenten over productconformiteit indienen om verwijdering van
  productvermeldingen te voorkomen</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
  Documenten over productconformiteit indienen om verwijdering van productvermeldingen te voorkomen
@@ -6045,39 +6638,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:06:50 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty
@@ -6091,39 +6684,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:58:32 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort
@@ -6138,39 +6731,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:54:06 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte
@@ -6184,39 +6777,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:50:08 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente
@@ -6231,39 +6824,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 15:58:40 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -6278,39 +6871,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Apr 2026 05:22:10 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -6329,39 +6922,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 11:10:42 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6377,39 +6970,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 05:38:32 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -6430,39 +7023,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:19:11 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -6480,40 +7073,40 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:18:24 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -6531,39 +7124,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:32 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6580,39 +7173,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:50 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -6630,40 +7223,40 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:30 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6681,39 +7274,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:22 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -6731,39 +7324,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 00:31:36 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -6780,39 +7373,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6827,39 +7420,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 07:42:42 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6878,39 +7471,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:32:20 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Prime Day：立即提报您的促销</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>Prime Day（日期待公布）：立即提报您的促销
 尊敬的卖家，
@@ -6928,39 +7521,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:19:47 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以重新启售商品</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品安全文件以重新启售商品
@@ -6999,39 +7592,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:42 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -7047,40 +7640,40 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:14 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -7096,39 +7689,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:36 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -7144,39 +7737,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:34 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -7190,40 +7783,40 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:11:30 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -7239,39 +7832,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:09:39 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -7287,39 +7880,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 05:22:42 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -7340,39 +7933,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 15:14:51 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -7387,39 +7980,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 09:39:52 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Verify your primary operating address for tax purposes</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  Verify your primary operating address for tax purposes
@@ -7436,39 +8029,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:10:49 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>[Formal Notice – Immediate Action Required] Review and certify your business information within 10 days to avoid account deactivation</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -7482,39 +8075,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:59:02 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Verkaeuferservice &lt;merch.service05@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12354633592] 其他账户问题</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴：
 您好！
@@ -7533,40 +8126,40 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:22:14 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Product Support Team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Reduce Returns &amp; Boost Customer Satisfaction - Enrol in Amazon
  Product Support</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
  Enrol now into Amazon Product Support !
@@ -7580,40 +8173,40 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 13:44:27 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -7631,39 +8224,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 01:52:13 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 Just a short follow-up regarding the [Vergleich.org](http://Vergleich.org)
@@ -7696,39 +8289,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 17:17:52 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Introducing Global Warehousing &amp; Distribution</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
  Store inventory at origin in China with lower costs and faster speeds.
@@ -7743,39 +8336,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 16:27:24 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 3/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -7794,39 +8387,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:49:51 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -7845,39 +8438,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:53:45 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán a medida que se procesen las unidades</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>96
  Las tarifas por retirada y puesta de inventario a disposición de Amazon de Logística de Amazon se cobrarán ahora por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición.
@@ -7889,39 +8482,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 09:19:33 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Opłaty za usunięcie i likwidację zapasów FBA naliczane podczas przetwarzania jednostek</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>96
  Opłaty za wycofanie i usunięcie zapasów w ramach FBA będą teraz pobierane od każdej jednostki w momencie jej wycofania lub usunięcia.
@@ -7937,39 +8530,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 08:46:52 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Addebito delle tariffe di rimozione e per reimpiego quando le unità vengono elaborate</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>96
  Le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno ora addebitate per unità ogni volta che un'unità viene rimossa o destinata ad altro uso.
@@ -7981,86 +8574,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 8 Apr 2026 15:00:43 +0000</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>Votre paiement est en cours</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Félicitations ! Votre paiement est en cours et arrivera sous peu.
- Tentative de versement
-Félicitations, Weihai EU ! Votre paiement est en cours et arrivera sous trois à cinq jours.
-Le 04/08/26 15:00 CEST, nous avons effectué un virement d’un montant de €
- 26.11 sur le compte lié à votre méthode de paiement (compte bancaire se terminant par 229).
- Si le montant est inférieur au montant auquel vous vous attendiez, voici quelques questions à vous poser :
- Disposez-vous d’un solde de fonds non disponibles ? Amazon peut réserver des fonds afin de couvrir des retours, des réclamations ou des rétrofacturations potentiels des acheteurs. Si tel est le cas, le solde de fin de période de votre rapport sur les paiements affichera le solde des fonds non disponibles réservé.
- Vos ventes couvraient-elles l’ensemble des frais et des retours pour cette période de règlements ? Le montant du paiement reflète votre activité commerciale, les frais de vente et les frais relatifs aux promotions et aux services. Nous vous recommandons de consulter votre rapport sur les paiements sous l’onglet Rapports de Seller Central pour comprendre votre solde de fin de pé</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 04:25:43 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8084,39 +8630,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 03:35:07 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-07</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8137,39 +8683,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-30</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8191,39 +8737,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 03:30:46 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8246,39 +8792,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-23</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8299,39 +8845,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:27:29 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8354,39 +8900,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 00:16:37 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -8416,39 +8962,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 18:05:15 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>提交商品合规文件，以避免商品被移除</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品合规文件，以避免商品被移除
@@ -8497,39 +9043,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 11:41:39 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>GTTC国际业务部玩具组 &lt;gttctoy@cngttc.cn&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>AMAZON DV TIC TRF ID--Top urgently</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>Dear Vendor,        Some of your TR numbers on Amazon have been pending in our backend for a long time without timely processing. We plan to automatically clear all unresponded TR numbers in our system two days later.
 If you have any TR numbers that require sample submission for testing, please reply to this email and send us the corresponding TR numbers within two days, and contact our relevant customer service within one week to arrange sample submission.
@@ -8538,39 +9084,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 02:18:44 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -8586,39 +9132,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
 C2S2 PCP Pallet Limited Time Promotion
@@ -8634,39 +9180,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
@@ -8686,39 +9232,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
